--- a/Resources/Variable_description_full.xlsx
+++ b/Resources/Variable_description_full.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="310" documentId="13_ncr:1_{2940B1FB-72E4-4F44-90D5-EDC63A843231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B58FF30-69F6-484E-9432-FA058BC2AF29}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="13_ncr:1_{2940B1FB-72E4-4F44-90D5-EDC63A843231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{808DE9D4-8036-4E20-8DBA-7DFAB0C8340B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3060" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="26" xr2:uid="{5AAFC457-EF6C-4291-BD55-176E067D6DA9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="8" xr2:uid="{5AAFC457-EF6C-4291-BD55-176E067D6DA9}"/>
   </bookViews>
   <sheets>
     <sheet name="Berge_cs" sheetId="1" r:id="rId1"/>
@@ -15,8 +15,8 @@
     <sheet name="Bernard_lake_eddypro" sheetId="15" r:id="rId5"/>
     <sheet name="Foret_est_cs" sheetId="6" r:id="rId6"/>
     <sheet name="Foret_est_eddypro" sheetId="13" r:id="rId7"/>
-    <sheet name="Foret_ouest_eddypro" sheetId="12" r:id="rId8"/>
-    <sheet name="Foret_ouest_cs" sheetId="5" r:id="rId9"/>
+    <sheet name="Foret_ouest_cs" sheetId="5" r:id="rId8"/>
+    <sheet name="Foret_ouest_eddypro" sheetId="12" r:id="rId9"/>
     <sheet name="Foret_sol_cs" sheetId="3" r:id="rId10"/>
     <sheet name="Foret_precip_cs" sheetId="17" r:id="rId11"/>
     <sheet name="Juvenile_NO_cs" sheetId="21" r:id="rId12"/>
@@ -5834,10 +5834,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66763,2425 +66759,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E191"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="27.54296875" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" customWidth="1"/>
-    <col min="3" max="3" width="129.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="109.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.8">
-      <c r="B1" s="7" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="18" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>668</v>
-      </c>
-      <c r="B6" t="s">
-        <v>668</v>
-      </c>
-      <c r="C6" t="s">
-        <v>829</v>
-      </c>
-      <c r="D6" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>670</v>
-      </c>
-      <c r="B7" t="s">
-        <v>670</v>
-      </c>
-      <c r="C7" t="s">
-        <v>830</v>
-      </c>
-      <c r="D7" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>672</v>
-      </c>
-      <c r="B8" t="s">
-        <v>672</v>
-      </c>
-      <c r="C8" t="s">
-        <v>831</v>
-      </c>
-      <c r="D8" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>915</v>
-      </c>
-      <c r="B9" t="s">
-        <v>666</v>
-      </c>
-      <c r="C9" t="s">
-        <v>828</v>
-      </c>
-      <c r="D9" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>934</v>
-      </c>
-      <c r="B10" t="s">
-        <v>680</v>
-      </c>
-      <c r="C10" t="s">
-        <v>837</v>
-      </c>
-      <c r="D10" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>933</v>
-      </c>
-      <c r="B11" t="s">
-        <v>678</v>
-      </c>
-      <c r="C11" t="s">
-        <v>836</v>
-      </c>
-      <c r="D11" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>914</v>
-      </c>
-      <c r="B12" t="s">
-        <v>665</v>
-      </c>
-      <c r="C12" t="s">
-        <v>827</v>
-      </c>
-      <c r="D12" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>935</v>
-      </c>
-      <c r="B13" t="s">
-        <v>682</v>
-      </c>
-      <c r="C13" t="s">
-        <v>839</v>
-      </c>
-      <c r="D13" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>932</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>838</v>
-      </c>
-      <c r="D14" t="s">
-        <v>667</v>
-      </c>
-      <c r="E14" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>700</v>
-      </c>
-      <c r="B15" t="s">
-        <v>700</v>
-      </c>
-      <c r="C15" t="s">
-        <v>852</v>
-      </c>
-      <c r="D15" t="s">
-        <v>634</v>
-      </c>
-      <c r="E15" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B16" t="s">
-        <v>969</v>
-      </c>
-      <c r="C16" t="s">
-        <v>794</v>
-      </c>
-      <c r="D16" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>896</v>
-      </c>
-      <c r="B17" t="s">
-        <v>968</v>
-      </c>
-      <c r="C17" t="s">
-        <v>797</v>
-      </c>
-      <c r="D17" t="s">
-        <v>634</v>
-      </c>
-      <c r="E17" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>897</v>
-      </c>
-      <c r="B18" t="s">
-        <v>970</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1200</v>
-      </c>
-      <c r="D18" t="s">
-        <v>798</v>
-      </c>
-      <c r="E18" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>910</v>
-      </c>
-      <c r="B19" t="s">
-        <v>971</v>
-      </c>
-      <c r="C19" t="s">
-        <v>824</v>
-      </c>
-      <c r="D19" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>908</v>
-      </c>
-      <c r="B20" t="s">
-        <v>972</v>
-      </c>
-      <c r="C20" t="s">
-        <v>822</v>
-      </c>
-      <c r="D20" t="s">
-        <v>653</v>
-      </c>
-      <c r="E20" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>909</v>
-      </c>
-      <c r="B21" t="s">
-        <v>973</v>
-      </c>
-      <c r="C21" t="s">
-        <v>823</v>
-      </c>
-      <c r="D21" t="s">
-        <v>799</v>
-      </c>
-      <c r="E21" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>913</v>
-      </c>
-      <c r="B22" t="s">
-        <v>974</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1204</v>
-      </c>
-      <c r="D22" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>899</v>
-      </c>
-      <c r="B23" t="s">
-        <v>975</v>
-      </c>
-      <c r="C23" t="s">
-        <v>809</v>
-      </c>
-      <c r="D23" t="s">
-        <v>798</v>
-      </c>
-      <c r="E23" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>894</v>
-      </c>
-      <c r="B24" t="s">
-        <v>983</v>
-      </c>
-      <c r="C24" t="s">
-        <v>792</v>
-      </c>
-      <c r="D24" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>893</v>
-      </c>
-      <c r="B25" t="s">
-        <v>984</v>
-      </c>
-      <c r="C25" t="s">
-        <v>795</v>
-      </c>
-      <c r="D25" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>895</v>
-      </c>
-      <c r="B26" t="s">
-        <v>985</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1201</v>
-      </c>
-      <c r="D26" t="s">
-        <v>798</v>
-      </c>
-      <c r="E26" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>902</v>
-      </c>
-      <c r="B27" t="s">
-        <v>986</v>
-      </c>
-      <c r="C27" t="s">
-        <v>816</v>
-      </c>
-      <c r="D27" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>900</v>
-      </c>
-      <c r="B28" t="s">
-        <v>987</v>
-      </c>
-      <c r="C28" t="s">
-        <v>813</v>
-      </c>
-      <c r="D28" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>901</v>
-      </c>
-      <c r="B29" t="s">
-        <v>988</v>
-      </c>
-      <c r="C29" t="s">
-        <v>815</v>
-      </c>
-      <c r="D29" t="s">
-        <v>799</v>
-      </c>
-      <c r="E29" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>903</v>
-      </c>
-      <c r="B30" t="s">
-        <v>989</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D30" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>898</v>
-      </c>
-      <c r="B31" t="s">
-        <v>990</v>
-      </c>
-      <c r="C31" t="s">
-        <v>807</v>
-      </c>
-      <c r="D31" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" t="s">
-        <v>802</v>
-      </c>
-      <c r="D32" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>71</v>
-      </c>
-      <c r="B33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" t="s">
-        <v>834</v>
-      </c>
-      <c r="D33" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>677</v>
-      </c>
-      <c r="B34" t="s">
-        <v>677</v>
-      </c>
-      <c r="C34" t="s">
-        <v>835</v>
-      </c>
-      <c r="D34" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>920</v>
-      </c>
-      <c r="B35" t="s">
-        <v>695</v>
-      </c>
-      <c r="C35" t="s">
-        <v>367</v>
-      </c>
-      <c r="D35" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" t="s">
-        <v>786</v>
-      </c>
-      <c r="D36" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>889</v>
-      </c>
-      <c r="B37" t="s">
-        <v>641</v>
-      </c>
-      <c r="C37" t="s">
-        <v>787</v>
-      </c>
-      <c r="D37" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>890</v>
-      </c>
-      <c r="B38" t="s">
-        <v>642</v>
-      </c>
-      <c r="C38" t="s">
-        <v>785</v>
-      </c>
-      <c r="D38" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>649</v>
-      </c>
-      <c r="B39" t="s">
-        <v>649</v>
-      </c>
-      <c r="C39" t="s">
-        <v>805</v>
-      </c>
-      <c r="D39" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>906</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C40" t="s">
-        <v>820</v>
-      </c>
-      <c r="D40" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>904</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C41" t="s">
-        <v>818</v>
-      </c>
-      <c r="D41" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>905</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C42" t="s">
-        <v>819</v>
-      </c>
-      <c r="D42" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>907</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D43" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>916</v>
-      </c>
-      <c r="B44" t="s">
-        <v>676</v>
-      </c>
-      <c r="C44" t="s">
-        <v>833</v>
-      </c>
-      <c r="D44" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" t="s">
-        <v>788</v>
-      </c>
-      <c r="D45" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>891</v>
-      </c>
-      <c r="B46" t="s">
-        <v>643</v>
-      </c>
-      <c r="C46" t="s">
-        <v>789</v>
-      </c>
-      <c r="D46" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>892</v>
-      </c>
-      <c r="B47" t="s">
-        <v>644</v>
-      </c>
-      <c r="C47" t="s">
-        <v>790</v>
-      </c>
-      <c r="D47" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>650</v>
-      </c>
-      <c r="B48" t="s">
-        <v>650</v>
-      </c>
-      <c r="C48" t="s">
-        <v>806</v>
-      </c>
-      <c r="D48" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>922</v>
-      </c>
-      <c r="B49" t="s">
-        <v>697</v>
-      </c>
-      <c r="C49" t="s">
-        <v>923</v>
-      </c>
-      <c r="D49" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>924</v>
-      </c>
-      <c r="B50" t="s">
-        <v>699</v>
-      </c>
-      <c r="C50" t="s">
-        <v>851</v>
-      </c>
-      <c r="D50" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>1124</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1130</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>925</v>
-      </c>
-      <c r="B54" t="s">
-        <v>701</v>
-      </c>
-      <c r="C54" t="s">
-        <v>538</v>
-      </c>
-      <c r="D54" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>636</v>
-      </c>
-      <c r="B55" t="s">
-        <v>636</v>
-      </c>
-      <c r="C55" t="s">
-        <v>783</v>
-      </c>
-      <c r="D55" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>886</v>
-      </c>
-      <c r="B56" t="s">
-        <v>638</v>
-      </c>
-      <c r="C56" t="s">
-        <v>784</v>
-      </c>
-      <c r="D56" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>888</v>
-      </c>
-      <c r="B57" t="s">
-        <v>639</v>
-      </c>
-      <c r="C57" t="s">
-        <v>785</v>
-      </c>
-      <c r="D57" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>385</v>
-      </c>
-      <c r="B58" t="s">
-        <v>181</v>
-      </c>
-      <c r="C58" t="s">
-        <v>194</v>
-      </c>
-      <c r="D58" t="s">
-        <v>195</v>
-      </c>
-      <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>921</v>
-      </c>
-      <c r="B59" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" t="s">
-        <v>850</v>
-      </c>
-      <c r="D59" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>635</v>
-      </c>
-      <c r="B60" t="s">
-        <v>635</v>
-      </c>
-      <c r="C60" t="s">
-        <v>782</v>
-      </c>
-      <c r="D60" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>927</v>
-      </c>
-      <c r="B61" t="s">
-        <v>692</v>
-      </c>
-      <c r="C61" t="s">
-        <v>853</v>
-      </c>
-      <c r="D61" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>928</v>
-      </c>
-      <c r="B62" t="s">
-        <v>691</v>
-      </c>
-      <c r="C62" t="s">
-        <v>847</v>
-      </c>
-      <c r="D62" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>926</v>
-      </c>
-      <c r="B63" t="s">
-        <v>690</v>
-      </c>
-      <c r="C63" t="s">
-        <v>846</v>
-      </c>
-      <c r="D63" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>917</v>
-      </c>
-      <c r="B64" t="s">
-        <v>687</v>
-      </c>
-      <c r="C64" t="s">
-        <v>843</v>
-      </c>
-      <c r="D64" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B65" t="s">
-        <v>768</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D65" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>918</v>
-      </c>
-      <c r="B66" t="s">
-        <v>688</v>
-      </c>
-      <c r="C66" t="s">
-        <v>844</v>
-      </c>
-      <c r="D66" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B67" t="s">
-        <v>769</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1122</v>
-      </c>
-      <c r="D67" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>919</v>
-      </c>
-      <c r="B68" t="s">
-        <v>689</v>
-      </c>
-      <c r="C68" t="s">
-        <v>845</v>
-      </c>
-      <c r="D68" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B69" t="s">
-        <v>770</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1123</v>
-      </c>
-      <c r="D69" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="36" x14ac:dyDescent="0.8">
-      <c r="B71" s="7" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B73" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" s="18" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A75" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>215</v>
-      </c>
-      <c r="B76" t="s">
-        <v>721</v>
-      </c>
-      <c r="D76" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>215</v>
-      </c>
-      <c r="B77" t="s">
-        <v>778</v>
-      </c>
-      <c r="D77" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>215</v>
-      </c>
-      <c r="B78" t="s">
-        <v>779</v>
-      </c>
-      <c r="D78" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>215</v>
-      </c>
-      <c r="B79" t="s">
-        <v>719</v>
-      </c>
-      <c r="D79" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>215</v>
-      </c>
-      <c r="B80" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>215</v>
-      </c>
-      <c r="B81" t="s">
-        <v>740</v>
-      </c>
-      <c r="D81" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>215</v>
-      </c>
-      <c r="B82" t="s">
-        <v>762</v>
-      </c>
-      <c r="D82" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>215</v>
-      </c>
-      <c r="B83" t="s">
-        <v>763</v>
-      </c>
-      <c r="D83" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>215</v>
-      </c>
-      <c r="B84" t="s">
-        <v>764</v>
-      </c>
-      <c r="D84" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>215</v>
-      </c>
-      <c r="B85" t="s">
-        <v>753</v>
-      </c>
-      <c r="D85" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>215</v>
-      </c>
-      <c r="B86" t="s">
-        <v>755</v>
-      </c>
-      <c r="D86" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>215</v>
-      </c>
-      <c r="B87" t="s">
-        <v>759</v>
-      </c>
-      <c r="D87" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>215</v>
-      </c>
-      <c r="B88" t="s">
-        <v>765</v>
-      </c>
-      <c r="D88" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>215</v>
-      </c>
-      <c r="B89" t="s">
-        <v>760</v>
-      </c>
-      <c r="D89" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>215</v>
-      </c>
-      <c r="B90" t="s">
-        <v>978</v>
-      </c>
-      <c r="C90" t="s">
-        <v>814</v>
-      </c>
-      <c r="D90" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>215</v>
-      </c>
-      <c r="B91" t="s">
-        <v>980</v>
-      </c>
-      <c r="C91" t="s">
-        <v>870</v>
-      </c>
-      <c r="D91" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>215</v>
-      </c>
-      <c r="B92" t="s">
-        <v>977</v>
-      </c>
-      <c r="C92" t="s">
-        <v>825</v>
-      </c>
-      <c r="D92" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>215</v>
-      </c>
-      <c r="B93" t="s">
-        <v>976</v>
-      </c>
-      <c r="C93" t="s">
-        <v>812</v>
-      </c>
-      <c r="D93" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>215</v>
-      </c>
-      <c r="B94" t="s">
-        <v>981</v>
-      </c>
-      <c r="D94" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>215</v>
-      </c>
-      <c r="B95" t="s">
-        <v>742</v>
-      </c>
-      <c r="D95" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>215</v>
-      </c>
-      <c r="B96" t="s">
-        <v>746</v>
-      </c>
-      <c r="D96" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>215</v>
-      </c>
-      <c r="B97" t="s">
-        <v>993</v>
-      </c>
-      <c r="C97" t="s">
-        <v>814</v>
-      </c>
-      <c r="D97" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>215</v>
-      </c>
-      <c r="B98" t="s">
-        <v>995</v>
-      </c>
-      <c r="C98" t="s">
-        <v>870</v>
-      </c>
-      <c r="D98" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>215</v>
-      </c>
-      <c r="B99" t="s">
-        <v>992</v>
-      </c>
-      <c r="C99" t="s">
-        <v>817</v>
-      </c>
-      <c r="D99" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>215</v>
-      </c>
-      <c r="B100" t="s">
-        <v>991</v>
-      </c>
-      <c r="C100" t="s">
-        <v>810</v>
-      </c>
-      <c r="D100" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>215</v>
-      </c>
-      <c r="B101" t="s">
-        <v>996</v>
-      </c>
-      <c r="D101" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>215</v>
-      </c>
-      <c r="B102" t="s">
-        <v>741</v>
-      </c>
-      <c r="D102" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>215</v>
-      </c>
-      <c r="B103" t="s">
-        <v>743</v>
-      </c>
-      <c r="D103" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>215</v>
-      </c>
-      <c r="B104" t="s">
-        <v>747</v>
-      </c>
-      <c r="D104" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>215</v>
-      </c>
-      <c r="B105" t="s">
-        <v>724</v>
-      </c>
-      <c r="D105" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>215</v>
-      </c>
-      <c r="B106" t="s">
-        <v>725</v>
-      </c>
-      <c r="D106" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>215</v>
-      </c>
-      <c r="B107" t="s">
-        <v>630</v>
-      </c>
-      <c r="C107" t="s">
-        <v>801</v>
-      </c>
-      <c r="D107" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>215</v>
-      </c>
-      <c r="B108" t="s">
-        <v>720</v>
-      </c>
-      <c r="D108" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109" t="s">
-        <v>215</v>
-      </c>
-      <c r="B109" t="s">
-        <v>674</v>
-      </c>
-      <c r="C109" t="s">
-        <v>832</v>
-      </c>
-      <c r="D109" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>215</v>
-      </c>
-      <c r="B110" t="s">
-        <v>633</v>
-      </c>
-      <c r="C110" t="s">
-        <v>791</v>
-      </c>
-      <c r="D110" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
-        <v>215</v>
-      </c>
-      <c r="B111" t="s">
-        <v>629</v>
-      </c>
-      <c r="C111" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
-        <v>215</v>
-      </c>
-      <c r="B112" t="s">
-        <v>713</v>
-      </c>
-      <c r="C112" t="s">
-        <v>866</v>
-      </c>
-      <c r="D112" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
-        <v>215</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C113" t="s">
-        <v>814</v>
-      </c>
-      <c r="D113" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
-        <v>215</v>
-      </c>
-      <c r="B114" t="s">
-        <v>998</v>
-      </c>
-      <c r="C114" t="s">
-        <v>793</v>
-      </c>
-      <c r="D114" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115" t="s">
-        <v>215</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C115" t="s">
-        <v>870</v>
-      </c>
-      <c r="D115" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>215</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C116" t="s">
-        <v>808</v>
-      </c>
-      <c r="D116" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
-        <v>215</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C117" t="s">
-        <v>821</v>
-      </c>
-      <c r="D117" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
-        <v>215</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C118" t="s">
-        <v>811</v>
-      </c>
-      <c r="D118" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119" t="s">
-        <v>215</v>
-      </c>
-      <c r="B119" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D119" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120" t="s">
-        <v>215</v>
-      </c>
-      <c r="B120" t="s">
-        <v>736</v>
-      </c>
-      <c r="D120" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>215</v>
-      </c>
-      <c r="B121" t="s">
-        <v>754</v>
-      </c>
-      <c r="D121" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
-        <v>215</v>
-      </c>
-      <c r="B122" t="s">
-        <v>715</v>
-      </c>
-      <c r="C122" t="s">
-        <v>868</v>
-      </c>
-      <c r="D122" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
-        <v>215</v>
-      </c>
-      <c r="B123" t="s">
-        <v>767</v>
-      </c>
-      <c r="D123" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>215</v>
-      </c>
-      <c r="B124" t="s">
-        <v>766</v>
-      </c>
-      <c r="D124" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>215</v>
-      </c>
-      <c r="B125" t="s">
-        <v>702</v>
-      </c>
-      <c r="C125" t="s">
-        <v>855</v>
-      </c>
-      <c r="D125" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>215</v>
-      </c>
-      <c r="B126" t="s">
-        <v>761</v>
-      </c>
-      <c r="D126" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>215</v>
-      </c>
-      <c r="B127" t="s">
-        <v>756</v>
-      </c>
-      <c r="D127" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>215</v>
-      </c>
-      <c r="B128" t="s">
-        <v>751</v>
-      </c>
-      <c r="D128" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>215</v>
-      </c>
-      <c r="B129" t="s">
-        <v>729</v>
-      </c>
-      <c r="D129" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>215</v>
-      </c>
-      <c r="B130" t="s">
-        <v>662</v>
-      </c>
-      <c r="D130" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>215</v>
-      </c>
-      <c r="B131" t="s">
-        <v>646</v>
-      </c>
-      <c r="D131" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>215</v>
-      </c>
-      <c r="B132" t="s">
-        <v>660</v>
-      </c>
-      <c r="D132" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>215</v>
-      </c>
-      <c r="B133" t="s">
-        <v>658</v>
-      </c>
-      <c r="D133" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>215</v>
-      </c>
-      <c r="B134" t="s">
-        <v>659</v>
-      </c>
-      <c r="D134" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>215</v>
-      </c>
-      <c r="B135" t="s">
-        <v>735</v>
-      </c>
-      <c r="D135" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>215</v>
-      </c>
-      <c r="B136" t="s">
-        <v>651</v>
-      </c>
-      <c r="D136" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>215</v>
-      </c>
-      <c r="B137" t="s">
-        <v>661</v>
-      </c>
-      <c r="D137" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>215</v>
-      </c>
-      <c r="B138" t="s">
-        <v>652</v>
-      </c>
-      <c r="D138" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>215</v>
-      </c>
-      <c r="B139" t="s">
-        <v>774</v>
-      </c>
-      <c r="D139" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>215</v>
-      </c>
-      <c r="B140" t="s">
-        <v>750</v>
-      </c>
-      <c r="D140" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>215</v>
-      </c>
-      <c r="B141" t="s">
-        <v>31</v>
-      </c>
-      <c r="C141" t="s">
-        <v>849</v>
-      </c>
-      <c r="D141" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>215</v>
-      </c>
-      <c r="B142" t="s">
-        <v>744</v>
-      </c>
-      <c r="D142" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>215</v>
-      </c>
-      <c r="B143" t="s">
-        <v>748</v>
-      </c>
-      <c r="D143" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>215</v>
-      </c>
-      <c r="B144" t="s">
-        <v>757</v>
-      </c>
-      <c r="C144" t="s">
-        <v>936</v>
-      </c>
-      <c r="D144" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>215</v>
-      </c>
-      <c r="B145" t="s">
-        <v>999</v>
-      </c>
-      <c r="C145" t="s">
-        <v>796</v>
-      </c>
-      <c r="D145" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>215</v>
-      </c>
-      <c r="B146" t="s">
-        <v>647</v>
-      </c>
-      <c r="D146" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>215</v>
-      </c>
-      <c r="B147" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C147" t="s">
-        <v>804</v>
-      </c>
-      <c r="D147" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>215</v>
-      </c>
-      <c r="B148" t="s">
-        <v>648</v>
-      </c>
-      <c r="D148" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>215</v>
-      </c>
-      <c r="B149" t="s">
-        <v>752</v>
-      </c>
-      <c r="D149" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>215</v>
-      </c>
-      <c r="B150" t="s">
-        <v>30</v>
-      </c>
-      <c r="C150" t="s">
-        <v>854</v>
-      </c>
-      <c r="D150" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>215</v>
-      </c>
-      <c r="B151" t="s">
-        <v>722</v>
-      </c>
-      <c r="D151" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>215</v>
-      </c>
-      <c r="B152" t="s">
-        <v>723</v>
-      </c>
-      <c r="D152" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>215</v>
-      </c>
-      <c r="B153" t="s">
-        <v>663</v>
-      </c>
-      <c r="C153" t="s">
-        <v>826</v>
-      </c>
-      <c r="D153" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>215</v>
-      </c>
-      <c r="B154" t="s">
-        <v>718</v>
-      </c>
-      <c r="D154" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>215</v>
-      </c>
-      <c r="B155" t="s">
-        <v>745</v>
-      </c>
-      <c r="D155" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>215</v>
-      </c>
-      <c r="B156" t="s">
-        <v>749</v>
-      </c>
-      <c r="D156" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>215</v>
-      </c>
-      <c r="B157" t="s">
-        <v>739</v>
-      </c>
-      <c r="D157" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>215</v>
-      </c>
-      <c r="B158" t="s">
-        <v>738</v>
-      </c>
-      <c r="D158" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>215</v>
-      </c>
-      <c r="B159" t="s">
-        <v>711</v>
-      </c>
-      <c r="C159" t="s">
-        <v>864</v>
-      </c>
-      <c r="D159" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>215</v>
-      </c>
-      <c r="B160" t="s">
-        <v>726</v>
-      </c>
-      <c r="D160" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>215</v>
-      </c>
-      <c r="B161" t="s">
-        <v>727</v>
-      </c>
-      <c r="D161" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>215</v>
-      </c>
-      <c r="B162" t="s">
-        <v>758</v>
-      </c>
-      <c r="D162" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>215</v>
-      </c>
-      <c r="B163" t="s">
-        <v>734</v>
-      </c>
-      <c r="D163" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>215</v>
-      </c>
-      <c r="B164" t="s">
-        <v>771</v>
-      </c>
-      <c r="D164" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>215</v>
-      </c>
-      <c r="B165" t="s">
-        <v>731</v>
-      </c>
-      <c r="C165" t="s">
-        <v>930</v>
-      </c>
-      <c r="D165" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>215</v>
-      </c>
-      <c r="B166" t="s">
-        <v>683</v>
-      </c>
-      <c r="C166" t="s">
-        <v>840</v>
-      </c>
-      <c r="D166" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>215</v>
-      </c>
-      <c r="B167" t="s">
-        <v>979</v>
-      </c>
-      <c r="C167" t="s">
-        <v>869</v>
-      </c>
-      <c r="D167" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>215</v>
-      </c>
-      <c r="B168" t="s">
-        <v>994</v>
-      </c>
-      <c r="C168" t="s">
-        <v>869</v>
-      </c>
-      <c r="D168" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>215</v>
-      </c>
-      <c r="B169" t="s">
-        <v>712</v>
-      </c>
-      <c r="C169" t="s">
-        <v>865</v>
-      </c>
-      <c r="D169" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>215</v>
-      </c>
-      <c r="B170" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C170" t="s">
-        <v>869</v>
-      </c>
-      <c r="D170" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>215</v>
-      </c>
-      <c r="B171" t="s">
-        <v>714</v>
-      </c>
-      <c r="C171" t="s">
-        <v>867</v>
-      </c>
-      <c r="D171" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>215</v>
-      </c>
-      <c r="B172" t="s">
-        <v>716</v>
-      </c>
-      <c r="D172" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>215</v>
-      </c>
-      <c r="B173" t="s">
-        <v>717</v>
-      </c>
-      <c r="D173" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>215</v>
-      </c>
-      <c r="B174" t="s">
-        <v>710</v>
-      </c>
-      <c r="C174" t="s">
-        <v>863</v>
-      </c>
-      <c r="D174" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>215</v>
-      </c>
-      <c r="B175" t="s">
-        <v>732</v>
-      </c>
-      <c r="C175" t="s">
-        <v>929</v>
-      </c>
-      <c r="D175" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>215</v>
-      </c>
-      <c r="B176" t="s">
-        <v>685</v>
-      </c>
-      <c r="C176" t="s">
-        <v>841</v>
-      </c>
-      <c r="D176" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>215</v>
-      </c>
-      <c r="B177" t="s">
-        <v>982</v>
-      </c>
-      <c r="D177" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>215</v>
-      </c>
-      <c r="B178" t="s">
-        <v>997</v>
-      </c>
-      <c r="D178" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>215</v>
-      </c>
-      <c r="B179" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D179" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>215</v>
-      </c>
-      <c r="B180" t="s">
-        <v>777</v>
-      </c>
-      <c r="D180" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>215</v>
-      </c>
-      <c r="B181" t="s">
-        <v>775</v>
-      </c>
-      <c r="D181" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>215</v>
-      </c>
-      <c r="B182" t="s">
-        <v>733</v>
-      </c>
-      <c r="C182" t="s">
-        <v>931</v>
-      </c>
-      <c r="D182" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>215</v>
-      </c>
-      <c r="B183" t="s">
-        <v>686</v>
-      </c>
-      <c r="C183" t="s">
-        <v>842</v>
-      </c>
-      <c r="D183" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>215</v>
-      </c>
-      <c r="B184" t="s">
-        <v>705</v>
-      </c>
-      <c r="C184" t="s">
-        <v>858</v>
-      </c>
-      <c r="D184" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>215</v>
-      </c>
-      <c r="B185" t="s">
-        <v>706</v>
-      </c>
-      <c r="C185" t="s">
-        <v>859</v>
-      </c>
-      <c r="D185" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>215</v>
-      </c>
-      <c r="B186" t="s">
-        <v>707</v>
-      </c>
-      <c r="C186" t="s">
-        <v>860</v>
-      </c>
-      <c r="D186" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>215</v>
-      </c>
-      <c r="B187" t="s">
-        <v>708</v>
-      </c>
-      <c r="C187" t="s">
-        <v>861</v>
-      </c>
-      <c r="D187" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>215</v>
-      </c>
-      <c r="B188" t="s">
-        <v>709</v>
-      </c>
-      <c r="C188" t="s">
-        <v>862</v>
-      </c>
-      <c r="D188" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>215</v>
-      </c>
-      <c r="B189" t="s">
-        <v>704</v>
-      </c>
-      <c r="C189" t="s">
-        <v>856</v>
-      </c>
-      <c r="D189" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>215</v>
-      </c>
-      <c r="B190" t="s">
-        <v>703</v>
-      </c>
-      <c r="C190" t="s">
-        <v>857</v>
-      </c>
-      <c r="D190" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>215</v>
-      </c>
-      <c r="B191" t="s">
-        <v>32</v>
-      </c>
-      <c r="C191" t="s">
-        <v>848</v>
-      </c>
-      <c r="D191" t="s">
-        <v>694</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G165"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -72256,4 +69833,2423 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E191"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.54296875" customWidth="1"/>
+    <col min="2" max="2" width="50.81640625" customWidth="1"/>
+    <col min="3" max="3" width="129.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="109.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="36" x14ac:dyDescent="0.8">
+      <c r="B1" s="7" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="18" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B6" t="s">
+        <v>668</v>
+      </c>
+      <c r="C6" t="s">
+        <v>829</v>
+      </c>
+      <c r="D6" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>670</v>
+      </c>
+      <c r="B7" t="s">
+        <v>670</v>
+      </c>
+      <c r="C7" t="s">
+        <v>830</v>
+      </c>
+      <c r="D7" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B8" t="s">
+        <v>672</v>
+      </c>
+      <c r="C8" t="s">
+        <v>831</v>
+      </c>
+      <c r="D8" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>915</v>
+      </c>
+      <c r="B9" t="s">
+        <v>666</v>
+      </c>
+      <c r="C9" t="s">
+        <v>828</v>
+      </c>
+      <c r="D9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>934</v>
+      </c>
+      <c r="B10" t="s">
+        <v>680</v>
+      </c>
+      <c r="C10" t="s">
+        <v>837</v>
+      </c>
+      <c r="D10" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>933</v>
+      </c>
+      <c r="B11" t="s">
+        <v>678</v>
+      </c>
+      <c r="C11" t="s">
+        <v>836</v>
+      </c>
+      <c r="D11" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>914</v>
+      </c>
+      <c r="B12" t="s">
+        <v>665</v>
+      </c>
+      <c r="C12" t="s">
+        <v>827</v>
+      </c>
+      <c r="D12" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>935</v>
+      </c>
+      <c r="B13" t="s">
+        <v>682</v>
+      </c>
+      <c r="C13" t="s">
+        <v>839</v>
+      </c>
+      <c r="D13" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>932</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>838</v>
+      </c>
+      <c r="D14" t="s">
+        <v>667</v>
+      </c>
+      <c r="E14" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>700</v>
+      </c>
+      <c r="B15" t="s">
+        <v>700</v>
+      </c>
+      <c r="C15" t="s">
+        <v>852</v>
+      </c>
+      <c r="D15" t="s">
+        <v>634</v>
+      </c>
+      <c r="E15" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" t="s">
+        <v>969</v>
+      </c>
+      <c r="C16" t="s">
+        <v>794</v>
+      </c>
+      <c r="D16" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>896</v>
+      </c>
+      <c r="B17" t="s">
+        <v>968</v>
+      </c>
+      <c r="C17" t="s">
+        <v>797</v>
+      </c>
+      <c r="D17" t="s">
+        <v>634</v>
+      </c>
+      <c r="E17" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>897</v>
+      </c>
+      <c r="B18" t="s">
+        <v>970</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D18" t="s">
+        <v>798</v>
+      </c>
+      <c r="E18" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>910</v>
+      </c>
+      <c r="B19" t="s">
+        <v>971</v>
+      </c>
+      <c r="C19" t="s">
+        <v>824</v>
+      </c>
+      <c r="D19" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>908</v>
+      </c>
+      <c r="B20" t="s">
+        <v>972</v>
+      </c>
+      <c r="C20" t="s">
+        <v>822</v>
+      </c>
+      <c r="D20" t="s">
+        <v>653</v>
+      </c>
+      <c r="E20" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>909</v>
+      </c>
+      <c r="B21" t="s">
+        <v>973</v>
+      </c>
+      <c r="C21" t="s">
+        <v>823</v>
+      </c>
+      <c r="D21" t="s">
+        <v>799</v>
+      </c>
+      <c r="E21" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>913</v>
+      </c>
+      <c r="B22" t="s">
+        <v>974</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D22" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>899</v>
+      </c>
+      <c r="B23" t="s">
+        <v>975</v>
+      </c>
+      <c r="C23" t="s">
+        <v>809</v>
+      </c>
+      <c r="D23" t="s">
+        <v>798</v>
+      </c>
+      <c r="E23" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>894</v>
+      </c>
+      <c r="B24" t="s">
+        <v>983</v>
+      </c>
+      <c r="C24" t="s">
+        <v>792</v>
+      </c>
+      <c r="D24" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>893</v>
+      </c>
+      <c r="B25" t="s">
+        <v>984</v>
+      </c>
+      <c r="C25" t="s">
+        <v>795</v>
+      </c>
+      <c r="D25" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>895</v>
+      </c>
+      <c r="B26" t="s">
+        <v>985</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D26" t="s">
+        <v>798</v>
+      </c>
+      <c r="E26" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>902</v>
+      </c>
+      <c r="B27" t="s">
+        <v>986</v>
+      </c>
+      <c r="C27" t="s">
+        <v>816</v>
+      </c>
+      <c r="D27" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>900</v>
+      </c>
+      <c r="B28" t="s">
+        <v>987</v>
+      </c>
+      <c r="C28" t="s">
+        <v>813</v>
+      </c>
+      <c r="D28" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>901</v>
+      </c>
+      <c r="B29" t="s">
+        <v>988</v>
+      </c>
+      <c r="C29" t="s">
+        <v>815</v>
+      </c>
+      <c r="D29" t="s">
+        <v>799</v>
+      </c>
+      <c r="E29" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>903</v>
+      </c>
+      <c r="B30" t="s">
+        <v>989</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D30" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>898</v>
+      </c>
+      <c r="B31" t="s">
+        <v>990</v>
+      </c>
+      <c r="C31" t="s">
+        <v>807</v>
+      </c>
+      <c r="D31" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" t="s">
+        <v>802</v>
+      </c>
+      <c r="D32" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
+        <v>834</v>
+      </c>
+      <c r="D33" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>677</v>
+      </c>
+      <c r="B34" t="s">
+        <v>677</v>
+      </c>
+      <c r="C34" t="s">
+        <v>835</v>
+      </c>
+      <c r="D34" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>920</v>
+      </c>
+      <c r="B35" t="s">
+        <v>695</v>
+      </c>
+      <c r="C35" t="s">
+        <v>367</v>
+      </c>
+      <c r="D35" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>786</v>
+      </c>
+      <c r="D36" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>889</v>
+      </c>
+      <c r="B37" t="s">
+        <v>641</v>
+      </c>
+      <c r="C37" t="s">
+        <v>787</v>
+      </c>
+      <c r="D37" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>890</v>
+      </c>
+      <c r="B38" t="s">
+        <v>642</v>
+      </c>
+      <c r="C38" t="s">
+        <v>785</v>
+      </c>
+      <c r="D38" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>649</v>
+      </c>
+      <c r="B39" t="s">
+        <v>649</v>
+      </c>
+      <c r="C39" t="s">
+        <v>805</v>
+      </c>
+      <c r="D39" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>906</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C40" t="s">
+        <v>820</v>
+      </c>
+      <c r="D40" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>904</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C41" t="s">
+        <v>818</v>
+      </c>
+      <c r="D41" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>905</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C42" t="s">
+        <v>819</v>
+      </c>
+      <c r="D42" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>907</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D43" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>916</v>
+      </c>
+      <c r="B44" t="s">
+        <v>676</v>
+      </c>
+      <c r="C44" t="s">
+        <v>833</v>
+      </c>
+      <c r="D44" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" t="s">
+        <v>788</v>
+      </c>
+      <c r="D45" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>891</v>
+      </c>
+      <c r="B46" t="s">
+        <v>643</v>
+      </c>
+      <c r="C46" t="s">
+        <v>789</v>
+      </c>
+      <c r="D46" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>892</v>
+      </c>
+      <c r="B47" t="s">
+        <v>644</v>
+      </c>
+      <c r="C47" t="s">
+        <v>790</v>
+      </c>
+      <c r="D47" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>650</v>
+      </c>
+      <c r="B48" t="s">
+        <v>650</v>
+      </c>
+      <c r="C48" t="s">
+        <v>806</v>
+      </c>
+      <c r="D48" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>922</v>
+      </c>
+      <c r="B49" t="s">
+        <v>697</v>
+      </c>
+      <c r="C49" t="s">
+        <v>923</v>
+      </c>
+      <c r="D49" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>924</v>
+      </c>
+      <c r="B50" t="s">
+        <v>699</v>
+      </c>
+      <c r="C50" t="s">
+        <v>851</v>
+      </c>
+      <c r="D50" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>925</v>
+      </c>
+      <c r="B54" t="s">
+        <v>701</v>
+      </c>
+      <c r="C54" t="s">
+        <v>538</v>
+      </c>
+      <c r="D54" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>636</v>
+      </c>
+      <c r="B55" t="s">
+        <v>636</v>
+      </c>
+      <c r="C55" t="s">
+        <v>783</v>
+      </c>
+      <c r="D55" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>886</v>
+      </c>
+      <c r="B56" t="s">
+        <v>638</v>
+      </c>
+      <c r="C56" t="s">
+        <v>784</v>
+      </c>
+      <c r="D56" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>888</v>
+      </c>
+      <c r="B57" t="s">
+        <v>639</v>
+      </c>
+      <c r="C57" t="s">
+        <v>785</v>
+      </c>
+      <c r="D57" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>385</v>
+      </c>
+      <c r="B58" t="s">
+        <v>181</v>
+      </c>
+      <c r="C58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D58" t="s">
+        <v>195</v>
+      </c>
+      <c r="E58" s="5"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>921</v>
+      </c>
+      <c r="B59" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" t="s">
+        <v>850</v>
+      </c>
+      <c r="D59" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>635</v>
+      </c>
+      <c r="B60" t="s">
+        <v>635</v>
+      </c>
+      <c r="C60" t="s">
+        <v>782</v>
+      </c>
+      <c r="D60" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>927</v>
+      </c>
+      <c r="B61" t="s">
+        <v>692</v>
+      </c>
+      <c r="C61" t="s">
+        <v>853</v>
+      </c>
+      <c r="D61" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>928</v>
+      </c>
+      <c r="B62" t="s">
+        <v>691</v>
+      </c>
+      <c r="C62" t="s">
+        <v>847</v>
+      </c>
+      <c r="D62" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>926</v>
+      </c>
+      <c r="B63" t="s">
+        <v>690</v>
+      </c>
+      <c r="C63" t="s">
+        <v>846</v>
+      </c>
+      <c r="D63" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>917</v>
+      </c>
+      <c r="B64" t="s">
+        <v>687</v>
+      </c>
+      <c r="C64" t="s">
+        <v>843</v>
+      </c>
+      <c r="D64" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B65" t="s">
+        <v>768</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D65" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>918</v>
+      </c>
+      <c r="B66" t="s">
+        <v>688</v>
+      </c>
+      <c r="C66" t="s">
+        <v>844</v>
+      </c>
+      <c r="D66" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B67" t="s">
+        <v>769</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D67" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>919</v>
+      </c>
+      <c r="B68" t="s">
+        <v>689</v>
+      </c>
+      <c r="C68" t="s">
+        <v>845</v>
+      </c>
+      <c r="D68" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B69" t="s">
+        <v>770</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D69" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="36" x14ac:dyDescent="0.8">
+      <c r="B71" s="7" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" s="18" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A75" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>215</v>
+      </c>
+      <c r="B76" t="s">
+        <v>721</v>
+      </c>
+      <c r="D76" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>215</v>
+      </c>
+      <c r="B77" t="s">
+        <v>778</v>
+      </c>
+      <c r="D77" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>215</v>
+      </c>
+      <c r="B78" t="s">
+        <v>779</v>
+      </c>
+      <c r="D78" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>215</v>
+      </c>
+      <c r="B79" t="s">
+        <v>719</v>
+      </c>
+      <c r="D79" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>215</v>
+      </c>
+      <c r="B80" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" t="s">
+        <v>740</v>
+      </c>
+      <c r="D81" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>215</v>
+      </c>
+      <c r="B82" t="s">
+        <v>762</v>
+      </c>
+      <c r="D82" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>215</v>
+      </c>
+      <c r="B83" t="s">
+        <v>763</v>
+      </c>
+      <c r="D83" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>215</v>
+      </c>
+      <c r="B84" t="s">
+        <v>764</v>
+      </c>
+      <c r="D84" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>215</v>
+      </c>
+      <c r="B85" t="s">
+        <v>753</v>
+      </c>
+      <c r="D85" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>215</v>
+      </c>
+      <c r="B86" t="s">
+        <v>755</v>
+      </c>
+      <c r="D86" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>215</v>
+      </c>
+      <c r="B87" t="s">
+        <v>759</v>
+      </c>
+      <c r="D87" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>215</v>
+      </c>
+      <c r="B88" t="s">
+        <v>765</v>
+      </c>
+      <c r="D88" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" t="s">
+        <v>760</v>
+      </c>
+      <c r="D89" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>215</v>
+      </c>
+      <c r="B90" t="s">
+        <v>978</v>
+      </c>
+      <c r="C90" t="s">
+        <v>814</v>
+      </c>
+      <c r="D90" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>215</v>
+      </c>
+      <c r="B91" t="s">
+        <v>980</v>
+      </c>
+      <c r="C91" t="s">
+        <v>870</v>
+      </c>
+      <c r="D91" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>215</v>
+      </c>
+      <c r="B92" t="s">
+        <v>977</v>
+      </c>
+      <c r="C92" t="s">
+        <v>825</v>
+      </c>
+      <c r="D92" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93" t="s">
+        <v>976</v>
+      </c>
+      <c r="C93" t="s">
+        <v>812</v>
+      </c>
+      <c r="D93" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>215</v>
+      </c>
+      <c r="B94" t="s">
+        <v>981</v>
+      </c>
+      <c r="D94" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>215</v>
+      </c>
+      <c r="B95" t="s">
+        <v>742</v>
+      </c>
+      <c r="D95" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" t="s">
+        <v>746</v>
+      </c>
+      <c r="D96" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" t="s">
+        <v>993</v>
+      </c>
+      <c r="C97" t="s">
+        <v>814</v>
+      </c>
+      <c r="D97" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>215</v>
+      </c>
+      <c r="B98" t="s">
+        <v>995</v>
+      </c>
+      <c r="C98" t="s">
+        <v>870</v>
+      </c>
+      <c r="D98" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" t="s">
+        <v>992</v>
+      </c>
+      <c r="C99" t="s">
+        <v>817</v>
+      </c>
+      <c r="D99" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>215</v>
+      </c>
+      <c r="B100" t="s">
+        <v>991</v>
+      </c>
+      <c r="C100" t="s">
+        <v>810</v>
+      </c>
+      <c r="D100" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>215</v>
+      </c>
+      <c r="B101" t="s">
+        <v>996</v>
+      </c>
+      <c r="D101" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>215</v>
+      </c>
+      <c r="B102" t="s">
+        <v>741</v>
+      </c>
+      <c r="D102" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>215</v>
+      </c>
+      <c r="B103" t="s">
+        <v>743</v>
+      </c>
+      <c r="D103" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>215</v>
+      </c>
+      <c r="B104" t="s">
+        <v>747</v>
+      </c>
+      <c r="D104" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>215</v>
+      </c>
+      <c r="B105" t="s">
+        <v>724</v>
+      </c>
+      <c r="D105" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>215</v>
+      </c>
+      <c r="B106" t="s">
+        <v>725</v>
+      </c>
+      <c r="D106" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>215</v>
+      </c>
+      <c r="B107" t="s">
+        <v>630</v>
+      </c>
+      <c r="C107" t="s">
+        <v>801</v>
+      </c>
+      <c r="D107" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>215</v>
+      </c>
+      <c r="B108" t="s">
+        <v>720</v>
+      </c>
+      <c r="D108" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>215</v>
+      </c>
+      <c r="B109" t="s">
+        <v>674</v>
+      </c>
+      <c r="C109" t="s">
+        <v>832</v>
+      </c>
+      <c r="D109" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>215</v>
+      </c>
+      <c r="B110" t="s">
+        <v>633</v>
+      </c>
+      <c r="C110" t="s">
+        <v>791</v>
+      </c>
+      <c r="D110" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>215</v>
+      </c>
+      <c r="B111" t="s">
+        <v>629</v>
+      </c>
+      <c r="C111" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>215</v>
+      </c>
+      <c r="B112" t="s">
+        <v>713</v>
+      </c>
+      <c r="C112" t="s">
+        <v>866</v>
+      </c>
+      <c r="D112" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>215</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C113" t="s">
+        <v>814</v>
+      </c>
+      <c r="D113" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>215</v>
+      </c>
+      <c r="B114" t="s">
+        <v>998</v>
+      </c>
+      <c r="C114" t="s">
+        <v>793</v>
+      </c>
+      <c r="D114" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>215</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C115" t="s">
+        <v>870</v>
+      </c>
+      <c r="D115" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>215</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C116" t="s">
+        <v>808</v>
+      </c>
+      <c r="D116" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>215</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C117" t="s">
+        <v>821</v>
+      </c>
+      <c r="D117" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>215</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C118" t="s">
+        <v>811</v>
+      </c>
+      <c r="D118" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>215</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D119" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>215</v>
+      </c>
+      <c r="B120" t="s">
+        <v>736</v>
+      </c>
+      <c r="D120" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>215</v>
+      </c>
+      <c r="B121" t="s">
+        <v>754</v>
+      </c>
+      <c r="D121" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>215</v>
+      </c>
+      <c r="B122" t="s">
+        <v>715</v>
+      </c>
+      <c r="C122" t="s">
+        <v>868</v>
+      </c>
+      <c r="D122" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>215</v>
+      </c>
+      <c r="B123" t="s">
+        <v>767</v>
+      </c>
+      <c r="D123" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>215</v>
+      </c>
+      <c r="B124" t="s">
+        <v>766</v>
+      </c>
+      <c r="D124" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
+        <v>702</v>
+      </c>
+      <c r="C125" t="s">
+        <v>855</v>
+      </c>
+      <c r="D125" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>215</v>
+      </c>
+      <c r="B126" t="s">
+        <v>761</v>
+      </c>
+      <c r="D126" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>215</v>
+      </c>
+      <c r="B127" t="s">
+        <v>756</v>
+      </c>
+      <c r="D127" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>215</v>
+      </c>
+      <c r="B128" t="s">
+        <v>751</v>
+      </c>
+      <c r="D128" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>215</v>
+      </c>
+      <c r="B129" t="s">
+        <v>729</v>
+      </c>
+      <c r="D129" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>215</v>
+      </c>
+      <c r="B130" t="s">
+        <v>662</v>
+      </c>
+      <c r="D130" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>215</v>
+      </c>
+      <c r="B131" t="s">
+        <v>646</v>
+      </c>
+      <c r="D131" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>215</v>
+      </c>
+      <c r="B132" t="s">
+        <v>660</v>
+      </c>
+      <c r="D132" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>215</v>
+      </c>
+      <c r="B133" t="s">
+        <v>658</v>
+      </c>
+      <c r="D133" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>215</v>
+      </c>
+      <c r="B134" t="s">
+        <v>659</v>
+      </c>
+      <c r="D134" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>215</v>
+      </c>
+      <c r="B135" t="s">
+        <v>735</v>
+      </c>
+      <c r="D135" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>215</v>
+      </c>
+      <c r="B136" t="s">
+        <v>651</v>
+      </c>
+      <c r="D136" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>215</v>
+      </c>
+      <c r="B137" t="s">
+        <v>661</v>
+      </c>
+      <c r="D137" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>215</v>
+      </c>
+      <c r="B138" t="s">
+        <v>652</v>
+      </c>
+      <c r="D138" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>215</v>
+      </c>
+      <c r="B139" t="s">
+        <v>774</v>
+      </c>
+      <c r="D139" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>215</v>
+      </c>
+      <c r="B140" t="s">
+        <v>750</v>
+      </c>
+      <c r="D140" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>215</v>
+      </c>
+      <c r="B141" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" t="s">
+        <v>849</v>
+      </c>
+      <c r="D141" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>215</v>
+      </c>
+      <c r="B142" t="s">
+        <v>744</v>
+      </c>
+      <c r="D142" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>215</v>
+      </c>
+      <c r="B143" t="s">
+        <v>748</v>
+      </c>
+      <c r="D143" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>215</v>
+      </c>
+      <c r="B144" t="s">
+        <v>757</v>
+      </c>
+      <c r="C144" t="s">
+        <v>936</v>
+      </c>
+      <c r="D144" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>215</v>
+      </c>
+      <c r="B145" t="s">
+        <v>999</v>
+      </c>
+      <c r="C145" t="s">
+        <v>796</v>
+      </c>
+      <c r="D145" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>215</v>
+      </c>
+      <c r="B146" t="s">
+        <v>647</v>
+      </c>
+      <c r="D146" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>215</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C147" t="s">
+        <v>804</v>
+      </c>
+      <c r="D147" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>215</v>
+      </c>
+      <c r="B148" t="s">
+        <v>648</v>
+      </c>
+      <c r="D148" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>215</v>
+      </c>
+      <c r="B149" t="s">
+        <v>752</v>
+      </c>
+      <c r="D149" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>215</v>
+      </c>
+      <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150" t="s">
+        <v>854</v>
+      </c>
+      <c r="D150" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>215</v>
+      </c>
+      <c r="B151" t="s">
+        <v>722</v>
+      </c>
+      <c r="D151" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>215</v>
+      </c>
+      <c r="B152" t="s">
+        <v>723</v>
+      </c>
+      <c r="D152" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>215</v>
+      </c>
+      <c r="B153" t="s">
+        <v>663</v>
+      </c>
+      <c r="C153" t="s">
+        <v>826</v>
+      </c>
+      <c r="D153" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>215</v>
+      </c>
+      <c r="B154" t="s">
+        <v>718</v>
+      </c>
+      <c r="D154" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>215</v>
+      </c>
+      <c r="B155" t="s">
+        <v>745</v>
+      </c>
+      <c r="D155" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>215</v>
+      </c>
+      <c r="B156" t="s">
+        <v>749</v>
+      </c>
+      <c r="D156" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>215</v>
+      </c>
+      <c r="B157" t="s">
+        <v>739</v>
+      </c>
+      <c r="D157" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>215</v>
+      </c>
+      <c r="B158" t="s">
+        <v>738</v>
+      </c>
+      <c r="D158" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>215</v>
+      </c>
+      <c r="B159" t="s">
+        <v>711</v>
+      </c>
+      <c r="C159" t="s">
+        <v>864</v>
+      </c>
+      <c r="D159" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>215</v>
+      </c>
+      <c r="B160" t="s">
+        <v>726</v>
+      </c>
+      <c r="D160" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>215</v>
+      </c>
+      <c r="B161" t="s">
+        <v>727</v>
+      </c>
+      <c r="D161" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>215</v>
+      </c>
+      <c r="B162" t="s">
+        <v>758</v>
+      </c>
+      <c r="D162" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>215</v>
+      </c>
+      <c r="B163" t="s">
+        <v>734</v>
+      </c>
+      <c r="D163" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>215</v>
+      </c>
+      <c r="B164" t="s">
+        <v>771</v>
+      </c>
+      <c r="D164" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>215</v>
+      </c>
+      <c r="B165" t="s">
+        <v>731</v>
+      </c>
+      <c r="C165" t="s">
+        <v>930</v>
+      </c>
+      <c r="D165" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>215</v>
+      </c>
+      <c r="B166" t="s">
+        <v>683</v>
+      </c>
+      <c r="C166" t="s">
+        <v>840</v>
+      </c>
+      <c r="D166" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>215</v>
+      </c>
+      <c r="B167" t="s">
+        <v>979</v>
+      </c>
+      <c r="C167" t="s">
+        <v>869</v>
+      </c>
+      <c r="D167" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>215</v>
+      </c>
+      <c r="B168" t="s">
+        <v>994</v>
+      </c>
+      <c r="C168" t="s">
+        <v>869</v>
+      </c>
+      <c r="D168" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>215</v>
+      </c>
+      <c r="B169" t="s">
+        <v>712</v>
+      </c>
+      <c r="C169" t="s">
+        <v>865</v>
+      </c>
+      <c r="D169" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>215</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C170" t="s">
+        <v>869</v>
+      </c>
+      <c r="D170" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>215</v>
+      </c>
+      <c r="B171" t="s">
+        <v>714</v>
+      </c>
+      <c r="C171" t="s">
+        <v>867</v>
+      </c>
+      <c r="D171" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>215</v>
+      </c>
+      <c r="B172" t="s">
+        <v>716</v>
+      </c>
+      <c r="D172" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>215</v>
+      </c>
+      <c r="B173" t="s">
+        <v>717</v>
+      </c>
+      <c r="D173" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>215</v>
+      </c>
+      <c r="B174" t="s">
+        <v>710</v>
+      </c>
+      <c r="C174" t="s">
+        <v>863</v>
+      </c>
+      <c r="D174" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>215</v>
+      </c>
+      <c r="B175" t="s">
+        <v>732</v>
+      </c>
+      <c r="C175" t="s">
+        <v>929</v>
+      </c>
+      <c r="D175" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>215</v>
+      </c>
+      <c r="B176" t="s">
+        <v>685</v>
+      </c>
+      <c r="C176" t="s">
+        <v>841</v>
+      </c>
+      <c r="D176" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>215</v>
+      </c>
+      <c r="B177" t="s">
+        <v>982</v>
+      </c>
+      <c r="D177" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>215</v>
+      </c>
+      <c r="B178" t="s">
+        <v>997</v>
+      </c>
+      <c r="D178" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>215</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D179" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>215</v>
+      </c>
+      <c r="B180" t="s">
+        <v>777</v>
+      </c>
+      <c r="D180" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>215</v>
+      </c>
+      <c r="B181" t="s">
+        <v>775</v>
+      </c>
+      <c r="D181" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>215</v>
+      </c>
+      <c r="B182" t="s">
+        <v>733</v>
+      </c>
+      <c r="C182" t="s">
+        <v>931</v>
+      </c>
+      <c r="D182" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>215</v>
+      </c>
+      <c r="B183" t="s">
+        <v>686</v>
+      </c>
+      <c r="C183" t="s">
+        <v>842</v>
+      </c>
+      <c r="D183" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>215</v>
+      </c>
+      <c r="B184" t="s">
+        <v>705</v>
+      </c>
+      <c r="C184" t="s">
+        <v>858</v>
+      </c>
+      <c r="D184" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>215</v>
+      </c>
+      <c r="B185" t="s">
+        <v>706</v>
+      </c>
+      <c r="C185" t="s">
+        <v>859</v>
+      </c>
+      <c r="D185" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>215</v>
+      </c>
+      <c r="B186" t="s">
+        <v>707</v>
+      </c>
+      <c r="C186" t="s">
+        <v>860</v>
+      </c>
+      <c r="D186" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>215</v>
+      </c>
+      <c r="B187" t="s">
+        <v>708</v>
+      </c>
+      <c r="C187" t="s">
+        <v>861</v>
+      </c>
+      <c r="D187" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>215</v>
+      </c>
+      <c r="B188" t="s">
+        <v>709</v>
+      </c>
+      <c r="C188" t="s">
+        <v>862</v>
+      </c>
+      <c r="D188" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>215</v>
+      </c>
+      <c r="B189" t="s">
+        <v>704</v>
+      </c>
+      <c r="C189" t="s">
+        <v>856</v>
+      </c>
+      <c r="D189" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>215</v>
+      </c>
+      <c r="B190" t="s">
+        <v>703</v>
+      </c>
+      <c r="C190" t="s">
+        <v>857</v>
+      </c>
+      <c r="D190" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>215</v>
+      </c>
+      <c r="B191" t="s">
+        <v>32</v>
+      </c>
+      <c r="C191" t="s">
+        <v>848</v>
+      </c>
+      <c r="D191" t="s">
+        <v>694</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>